--- a/public/templates/invigilation-class-template.xlsx
+++ b/public/templates/invigilation-class-template.xlsx
@@ -227,7 +227,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -254,9 +254,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -598,7 +595,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L27"/>
+  <dimension ref="A1:L40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18.875" customWidth="1"/>
@@ -1008,49 +1005,231 @@
       <c r="A25" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B25" s="10"/>
+      <c r="B25" s="8"/>
       <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
+      <c r="D25" s="9"/>
       <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
+      <c r="F25" s="9"/>
       <c r="G25" s="6"/>
-      <c r="H25" s="6"/>
-      <c r="I25" s="10"/>
+      <c r="H25" s="9"/>
+      <c r="I25" s="8"/>
       <c r="J25" s="6"/>
-      <c r="K25" s="6"/>
+      <c r="K25" s="9"/>
       <c r="L25" s="6"/>
     </row>
     <row r="26" ht="90" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B26" s="10"/>
+      <c r="B26" s="8"/>
       <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
+      <c r="D26" s="9"/>
       <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
+      <c r="F26" s="9"/>
       <c r="G26" s="6"/>
-      <c r="H26" s="6"/>
-      <c r="I26" s="10"/>
+      <c r="H26" s="9"/>
+      <c r="I26" s="8"/>
       <c r="J26" s="6"/>
-      <c r="K26" s="6"/>
+      <c r="K26" s="9"/>
       <c r="L26" s="6"/>
     </row>
     <row r="27" ht="90" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B27" s="10"/>
+      <c r="B27" s="8"/>
       <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
+      <c r="D27" s="9"/>
       <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
+      <c r="F27" s="9"/>
       <c r="G27" s="6"/>
-      <c r="H27" s="6"/>
-      <c r="I27" s="10"/>
+      <c r="H27" s="9"/>
+      <c r="I27" s="8"/>
       <c r="J27" s="6"/>
-      <c r="K27" s="6"/>
+      <c r="K27" s="9"/>
       <c r="L27" s="6"/>
+    </row>
+    <row r="28" ht="90" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A28" s="7"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="6"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="6"/>
+      <c r="H28" s="9"/>
+      <c r="I28" s="8"/>
+      <c r="J28" s="6"/>
+      <c r="K28" s="9"/>
+      <c r="L28" s="6"/>
+    </row>
+    <row r="29" ht="90" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29" s="7"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="6"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="9"/>
+      <c r="G29" s="6"/>
+      <c r="H29" s="9"/>
+      <c r="I29" s="8"/>
+      <c r="J29" s="6"/>
+      <c r="K29" s="9"/>
+      <c r="L29" s="6"/>
+    </row>
+    <row r="30" ht="90" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" s="7"/>
+      <c r="B30" s="8"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="9"/>
+      <c r="G30" s="6"/>
+      <c r="H30" s="9"/>
+      <c r="I30" s="8"/>
+      <c r="J30" s="6"/>
+      <c r="K30" s="9"/>
+      <c r="L30" s="6"/>
+    </row>
+    <row r="31" ht="90" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31" s="7"/>
+      <c r="B31" s="8"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="6"/>
+      <c r="H31" s="9"/>
+      <c r="I31" s="8"/>
+      <c r="J31" s="6"/>
+      <c r="K31" s="9"/>
+      <c r="L31" s="6"/>
+    </row>
+    <row r="32" ht="90" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A32" s="7"/>
+      <c r="B32" s="8"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="9"/>
+      <c r="G32" s="6"/>
+      <c r="H32" s="9"/>
+      <c r="I32" s="8"/>
+      <c r="J32" s="6"/>
+      <c r="K32" s="9"/>
+      <c r="L32" s="6"/>
+    </row>
+    <row r="33" ht="90" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A33" s="7"/>
+      <c r="B33" s="8"/>
+      <c r="C33" s="6"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="9"/>
+      <c r="G33" s="6"/>
+      <c r="H33" s="9"/>
+      <c r="I33" s="8"/>
+      <c r="J33" s="6"/>
+      <c r="K33" s="9"/>
+      <c r="L33" s="6"/>
+    </row>
+    <row r="34" ht="90" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A34" s="7"/>
+      <c r="B34" s="8"/>
+      <c r="C34" s="6"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="9"/>
+      <c r="G34" s="6"/>
+      <c r="H34" s="9"/>
+      <c r="I34" s="8"/>
+      <c r="J34" s="6"/>
+      <c r="K34" s="9"/>
+      <c r="L34" s="6"/>
+    </row>
+    <row r="35" ht="90" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A35" s="7"/>
+      <c r="B35" s="8"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="9"/>
+      <c r="G35" s="6"/>
+      <c r="H35" s="9"/>
+      <c r="I35" s="8"/>
+      <c r="J35" s="6"/>
+      <c r="K35" s="9"/>
+      <c r="L35" s="6"/>
+    </row>
+    <row r="36" ht="90" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A36" s="7"/>
+      <c r="B36" s="8"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="9"/>
+      <c r="G36" s="6"/>
+      <c r="H36" s="9"/>
+      <c r="I36" s="8"/>
+      <c r="J36" s="6"/>
+      <c r="K36" s="9"/>
+      <c r="L36" s="6"/>
+    </row>
+    <row r="37" ht="90" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A37" s="7"/>
+      <c r="B37" s="8"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="9"/>
+      <c r="G37" s="6"/>
+      <c r="H37" s="9"/>
+      <c r="I37" s="8"/>
+      <c r="J37" s="6"/>
+      <c r="K37" s="9"/>
+      <c r="L37" s="6"/>
+    </row>
+    <row r="38" ht="90" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A38" s="7"/>
+      <c r="B38" s="8"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="9"/>
+      <c r="G38" s="6"/>
+      <c r="H38" s="9"/>
+      <c r="I38" s="8"/>
+      <c r="J38" s="6"/>
+      <c r="K38" s="9"/>
+      <c r="L38" s="6"/>
+    </row>
+    <row r="39" ht="90" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A39" s="7"/>
+      <c r="B39" s="8"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="9"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="9"/>
+      <c r="G39" s="6"/>
+      <c r="H39" s="9"/>
+      <c r="I39" s="8"/>
+      <c r="J39" s="6"/>
+      <c r="K39" s="9"/>
+      <c r="L39" s="6"/>
+    </row>
+    <row r="40" ht="90" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A40" s="7"/>
+      <c r="B40" s="8"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="9"/>
+      <c r="G40" s="6"/>
+      <c r="H40" s="9"/>
+      <c r="I40" s="8"/>
+      <c r="J40" s="6"/>
+      <c r="K40" s="9"/>
+      <c r="L40" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/public/templates/invigilation-class-template.xlsx
+++ b/public/templates/invigilation-class-template.xlsx
@@ -595,12 +595,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L40"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18.875" customWidth="1"/>
     <col min="2" max="12" width="45.625" customWidth="1"/>
-    <col min="13" max="14" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="54.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -1049,188 +1048,6 @@
       <c r="K27" s="9"/>
       <c r="L27" s="6"/>
     </row>
-    <row r="28" ht="90" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28" s="7"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="6"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="8"/>
-      <c r="J28" s="6"/>
-      <c r="K28" s="9"/>
-      <c r="L28" s="6"/>
-    </row>
-    <row r="29" ht="90" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A29" s="7"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="6"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="6"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="6"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="8"/>
-      <c r="J29" s="6"/>
-      <c r="K29" s="9"/>
-      <c r="L29" s="6"/>
-    </row>
-    <row r="30" ht="90" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30" s="7"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="6"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="6"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="8"/>
-      <c r="J30" s="6"/>
-      <c r="K30" s="9"/>
-      <c r="L30" s="6"/>
-    </row>
-    <row r="31" ht="90" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31" s="7"/>
-      <c r="B31" s="8"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="8"/>
-      <c r="J31" s="6"/>
-      <c r="K31" s="9"/>
-      <c r="L31" s="6"/>
-    </row>
-    <row r="32" ht="90" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A32" s="7"/>
-      <c r="B32" s="8"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="6"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="8"/>
-      <c r="J32" s="6"/>
-      <c r="K32" s="9"/>
-      <c r="L32" s="6"/>
-    </row>
-    <row r="33" ht="90" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33" s="7"/>
-      <c r="B33" s="8"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="6"/>
-      <c r="H33" s="9"/>
-      <c r="I33" s="8"/>
-      <c r="J33" s="6"/>
-      <c r="K33" s="9"/>
-      <c r="L33" s="6"/>
-    </row>
-    <row r="34" ht="90" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A34" s="7"/>
-      <c r="B34" s="8"/>
-      <c r="C34" s="6"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="6"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="6"/>
-      <c r="H34" s="9"/>
-      <c r="I34" s="8"/>
-      <c r="J34" s="6"/>
-      <c r="K34" s="9"/>
-      <c r="L34" s="6"/>
-    </row>
-    <row r="35" ht="90" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A35" s="7"/>
-      <c r="B35" s="8"/>
-      <c r="C35" s="6"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="9"/>
-      <c r="I35" s="8"/>
-      <c r="J35" s="6"/>
-      <c r="K35" s="9"/>
-      <c r="L35" s="6"/>
-    </row>
-    <row r="36" ht="90" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A36" s="7"/>
-      <c r="B36" s="8"/>
-      <c r="C36" s="6"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="6"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="9"/>
-      <c r="I36" s="8"/>
-      <c r="J36" s="6"/>
-      <c r="K36" s="9"/>
-      <c r="L36" s="6"/>
-    </row>
-    <row r="37" ht="90" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A37" s="7"/>
-      <c r="B37" s="8"/>
-      <c r="C37" s="6"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="6"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="9"/>
-      <c r="I37" s="8"/>
-      <c r="J37" s="6"/>
-      <c r="K37" s="9"/>
-      <c r="L37" s="6"/>
-    </row>
-    <row r="38" ht="90" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A38" s="7"/>
-      <c r="B38" s="8"/>
-      <c r="C38" s="6"/>
-      <c r="D38" s="9"/>
-      <c r="E38" s="6"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="9"/>
-      <c r="I38" s="8"/>
-      <c r="J38" s="6"/>
-      <c r="K38" s="9"/>
-      <c r="L38" s="6"/>
-    </row>
-    <row r="39" ht="90" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A39" s="7"/>
-      <c r="B39" s="8"/>
-      <c r="C39" s="6"/>
-      <c r="D39" s="9"/>
-      <c r="E39" s="6"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="9"/>
-      <c r="I39" s="8"/>
-      <c r="J39" s="6"/>
-      <c r="K39" s="9"/>
-      <c r="L39" s="6"/>
-    </row>
-    <row r="40" ht="90" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A40" s="7"/>
-      <c r="B40" s="8"/>
-      <c r="C40" s="6"/>
-      <c r="D40" s="9"/>
-      <c r="E40" s="6"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="6"/>
-      <c r="H40" s="9"/>
-      <c r="I40" s="8"/>
-      <c r="J40" s="6"/>
-      <c r="K40" s="9"/>
-      <c r="L40" s="6"/>
-    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B1:H1"/>
